--- a/SysSettings.xlsx
+++ b/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VS_CEA_8C\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6003FC55-C02A-4524-9501-60F8F57311D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6562460F-4EC6-4A4F-BA3B-031F3D256599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="21600" windowHeight="12773" firstSheet="22" activeTab="28" xr2:uid="{0D8BD6A0-88C6-4920-BDDA-19ACAF08635D}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12772" firstSheet="22" activeTab="28" xr2:uid="{2ED43933-C1E9-4BA2-B0FF-F5E4A87661BE}"/>
   </bookViews>
   <sheets>
     <sheet name="heat_FRA" sheetId="2" r:id="rId1"/>
@@ -5507,15 +5507,15 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="4" applyFont="1"/>
   </cellXfs>
   <cellStyles count="9">
-    <cellStyle name="20% - Accent3 2 10" xfId="6" xr:uid="{833D9707-1A8C-4CEA-A551-0A458D0D9D30}"/>
-    <cellStyle name="20% - Accent3 2 13" xfId="5" xr:uid="{06E383E0-9B93-4B52-BB09-9E9FF0E9FA29}"/>
-    <cellStyle name="20% - Accent6 2 7" xfId="7" xr:uid="{70200A7B-1805-4180-A0A4-128F496396FC}"/>
+    <cellStyle name="20% - Accent3 2 10" xfId="6" xr:uid="{6230D1A3-9D91-40C9-B0C5-9D9BA03B145D}"/>
+    <cellStyle name="20% - Accent3 2 13" xfId="5" xr:uid="{499011C1-C7FE-44AF-8700-9BDFD45E2787}"/>
+    <cellStyle name="20% - Accent6 2 7" xfId="7" xr:uid="{8CBB1442-81CF-4F17-8A5E-62F5FAFCBFD0}"/>
     <cellStyle name="Heading 2" xfId="1" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="2" builtinId="18"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="8" xr:uid="{E42D4E3A-4DDE-47DF-AAD3-4735CA1F606F}"/>
-    <cellStyle name="Normal 39" xfId="3" xr:uid="{A3A51874-CD14-4C95-897C-B9A0588407B9}"/>
-    <cellStyle name="Normal 40" xfId="4" xr:uid="{32970D4B-B443-4359-BE12-69B7FC4E6718}"/>
+    <cellStyle name="Normal 2" xfId="8" xr:uid="{201AA820-249B-4978-BE06-FE9EA053915D}"/>
+    <cellStyle name="Normal 39" xfId="3" xr:uid="{86A5B341-7378-4DCC-AD9E-16E413253C06}"/>
+    <cellStyle name="Normal 40" xfId="4" xr:uid="{97C149DC-9F7B-4923-A697-8C2E38DE22A8}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -5550,7 +5550,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4D130B1-9766-4192-8104-96222B3AC30E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43463D7B-6CD7-4C23-995A-91793EA6509B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5905,7 +5905,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{764A38F7-21A8-4A40-8874-C1BA214CC7E1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1473A3F7-3F3C-4763-BFFC-2497D9FBF086}">
   <dimension ref="B3:I38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6830,7 +6830,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51C75033-E22D-4F62-8C81-6EAE55694A0D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15C9A664-2784-493F-B433-1D5DF855DEDE}">
   <dimension ref="B3:I41"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7833,7 +7833,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E88232C-A024-4A71-AB0B-6FAB80A7426D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AD4CF94-947F-4956-B10F-F0E3C96F5A6D}">
   <dimension ref="B3:I41"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8836,7 +8836,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02F5F6AA-0C1E-424A-9D13-07F665E7AC45}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8EF6181-556C-4419-BC74-594D5C119913}">
   <dimension ref="B3:S59"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -10557,7 +10557,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9A98343-87A6-4BA8-A05E-8EC0AC53E0EA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B95E3F62-77CA-41B7-BB4D-38D4E62F641D}">
   <dimension ref="B3:I27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11196,7 +11196,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEECFE78-6B35-4F4F-B41B-4633D4B9ABE5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29A9239B-6DD7-4CA8-B1F2-1C85AB051720}">
   <dimension ref="B3:I27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11835,7 +11835,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542E30C8-B39F-4C0F-9396-63766FAAEE46}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CA69009-1D77-4EF3-8E2A-1469462F00C9}">
   <dimension ref="B3:S43"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -12691,7 +12691,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31275141-614F-44C6-9B55-46080A71A7B8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{336AF936-99E4-41FD-825A-F03C152CBDA5}">
   <dimension ref="B3:I29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -13382,7 +13382,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AAEEE5C-532D-44D7-AE8B-9DF5382FE4A0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B77A1C4-FAD7-441F-86E1-D5857CA4FBC0}">
   <dimension ref="B3:I29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14073,7 +14073,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C20185BD-BFC5-45C9-A961-6B4DF7B17852}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB349AF8-6C46-4961-95A4-661CA3FDF046}">
   <dimension ref="B3:S67"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -15978,7 +15978,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5C32921-B610-4097-8764-025C57CD4730}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF0F6F20-2EF3-4832-AE65-00364B9D5207}">
   <dimension ref="B3:I21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -16461,7 +16461,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BA47ECC-BAAF-4914-AADB-229B8449A1C6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA4696B2-261E-4F25-92A6-FB60EF4B7C39}">
   <dimension ref="B3:I38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17386,7 +17386,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ECC3741-F019-415F-926E-A511D970EBD0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A10543DC-3C0D-4ECD-A0A2-1DC860C2DB8E}">
   <dimension ref="B3:I21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17869,7 +17869,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{974C7E90-BD65-4660-9650-49BB77424CDF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D25181E-FFC2-4C26-A645-AC6919AFF077}">
   <dimension ref="B3:S74"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -19935,7 +19935,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ED422E4-AAD9-438E-AD71-7FFBAA7E2742}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEEB932C-35E8-4A77-BB75-81D5FA74D35B}">
   <dimension ref="B3:I17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -20314,7 +20314,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA922C48-39C9-466F-9A83-B76C95E1F8C6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D54FC3F-82D9-4504-A8B3-3B7F5995DD8C}">
   <dimension ref="B3:I17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -20693,7 +20693,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{418A39FD-BF0C-49DD-91B5-98ABA6FCB2BA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B53F033-CB33-49D6-BAA1-D5EFAF265079}">
   <dimension ref="B3:S43"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -21742,7 +21742,7 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F33734BD-4AD8-46BE-9C7D-C2904D20C99E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35BB0D59-F778-458E-BF44-C49E4A163BEE}">
   <dimension ref="B2:H11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -21842,7 +21842,7 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C061562E-E4D4-4A09-9F4D-407C641C82A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAAC50B5-A97D-49E7-8270-4582C482CBB2}">
   <dimension ref="B3:G33"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
@@ -22120,7 +22120,7 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E50CEEB0-F105-4766-9E90-59146712B636}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3B67132-D7C7-4688-8CB0-900E5DAAC674}">
   <dimension ref="B1:N42"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
@@ -22706,7 +22706,7 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F3EE488-CF56-4802-BBAE-447110612217}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7056B708-1B45-4B98-931C-A30187FB8E2C}">
   <dimension ref="A2:N102"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
@@ -24346,7 +24346,7 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4835695-F085-4443-8EC6-CDB0FB5B47EE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A075746-8083-4AE5-A0E6-0A0521F4A518}">
   <dimension ref="B3:D33"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
@@ -24625,7 +24625,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96AE6ACF-5FFB-4F8E-AAC5-80C55EB52429}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{851C98D9-A4FF-4B22-9290-8CB157DBB355}">
   <dimension ref="B3:S79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -26806,7 +26806,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1D2F63B-4E2C-465D-979C-6EB39F139BA0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E9424F3-7278-4184-9CC8-F206584DEF24}">
   <dimension ref="B3:I19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27237,7 +27237,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{276F7EA0-DFDB-49A9-96C5-D51CF8BEC4DD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDA67C10-10D5-4817-B166-EA9EB8703D3C}">
   <dimension ref="B3:I19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27668,7 +27668,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BFFAF41-D52E-4BF1-8F4D-E8F4124DD345}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{758FC851-AFE0-4B8B-B27D-4A4BD749E406}">
   <dimension ref="B3:S80"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -29872,7 +29872,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA7C8AF8-CCB5-4B2F-8316-571C9A63BBB0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFEE6E5E-41E4-49A7-B5D7-7CEF95DD16F7}">
   <dimension ref="B3:I15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -30199,7 +30199,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{139A3894-EB8A-458D-8B8E-E6075CBCE214}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E9779CF-855F-4C66-AE3F-CED532C97A2C}">
   <dimension ref="B3:I15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -30526,7 +30526,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4CE6E8F-F9FD-425D-AB83-686F0C3199D4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F5C1853-1E4B-4BB3-9B4E-46B58DCCD260}">
   <dimension ref="B3:S43"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>

--- a/SysSettings.xlsx
+++ b/SysSettings.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VS_CEA_8C\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NewVEDA\Veda_models\VS_CEA_8C\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AA65BA5-2D2F-4C06-8794-65404A92A5EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC2885C-5CC6-402A-929C-0613A77186CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12772" firstSheet="21" activeTab="28" xr2:uid="{39196811-3449-4F1E-91A9-CEFB9A4676E0}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" firstSheet="21" activeTab="23" xr2:uid="{39196811-3449-4F1E-91A9-CEFB9A4676E0}"/>
   </bookViews>
   <sheets>
     <sheet name="heat_FRA" sheetId="2" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7328" uniqueCount="1753">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7333" uniqueCount="1755">
   <si>
     <t>~fi_comm</t>
   </si>
@@ -5323,6 +5323,12 @@
   </si>
   <si>
     <t>vervestacksMR</t>
+  </si>
+  <si>
+    <t>ELCnH</t>
+  </si>
+  <si>
+    <t>&gt;10 hours of surplus electricity from VRE generation</t>
   </si>
 </sst>
 </file>
@@ -20738,14 +20744,11 @@
       </c>
     </row>
     <row r="42" spans="2:19" x14ac:dyDescent="0.45">
-      <c r="B42" t="s">
-        <v>229</v>
-      </c>
       <c r="C42" t="s">
-        <v>283</v>
+        <v>1753</v>
       </c>
       <c r="D42" t="s">
-        <v>284</v>
+        <v>1754</v>
       </c>
       <c r="E42" t="s">
         <v>275</v>
@@ -20753,6 +20756,9 @@
       <c r="F42" t="s">
         <v>276</v>
       </c>
+      <c r="G42" t="s">
+        <v>85</v>
+      </c>
       <c r="M42" t="s">
         <v>9</v>
       </c>
@@ -20776,17 +20782,20 @@
       </c>
     </row>
     <row r="43" spans="2:19" x14ac:dyDescent="0.45">
+      <c r="B43" t="s">
+        <v>229</v>
+      </c>
       <c r="C43" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D43" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E43" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="F43" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="M43" t="s">
         <v>9</v>
@@ -20811,6 +20820,18 @@
       </c>
     </row>
     <row r="44" spans="2:19" x14ac:dyDescent="0.45">
+      <c r="C44" t="s">
+        <v>287</v>
+      </c>
+      <c r="D44" t="s">
+        <v>288</v>
+      </c>
+      <c r="E44" t="s">
+        <v>289</v>
+      </c>
+      <c r="F44" t="s">
+        <v>290</v>
+      </c>
       <c r="M44" t="s">
         <v>9</v>
       </c>
